--- a/data/gravel/Argonaut GR3 2023.xlsx
+++ b/data/gravel/Argonaut GR3 2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB0925C-051F-9A4C-A779-C284A5144493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41245D97-2C78-5E41-88CD-A6D62AD68248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25980" yWindow="-17280" windowWidth="25640" windowHeight="14600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="97">
   <si>
     <t>brand</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>a8:j32</t>
+  </si>
+  <si>
+    <t>https://argonautcycles.com/wp-content/uploads/2024/11/supernaut_home_small_GR3-scaled.jpg</t>
   </si>
 </sst>
 </file>
@@ -700,6 +703,11 @@
         <v>75</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>96</v>
+      </c>
+    </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Argonaut GR3 2023.xlsx
+++ b/data/gravel/Argonaut GR3 2023.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41245D97-2C78-5E41-88CD-A6D62AD68248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51F7854-49F7-FC4F-852D-8DB5FA9F7278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10420" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="99">
   <si>
     <t>brand</t>
   </si>
@@ -304,13 +304,19 @@
     <t>trail</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>a8:j32</t>
   </si>
   <si>
     <t>https://argonautcycles.com/wp-content/uploads/2024/11/supernaut_home_small_GR3-scaled.jpg</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bend, Oregon, USA</t>
   </si>
 </sst>
 </file>
@@ -657,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -705,7 +711,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -713,7 +719,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1555,7 +1561,15 @@
         <v>68</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>97</v>
+      </c>
+      <c r="B73" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
